--- a/artfynd/A 11088-2026 artfynd.xlsx
+++ b/artfynd/A 11088-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129523499</v>
+        <v>108306000</v>
       </c>
       <c r="B2" t="n">
-        <v>58166</v>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bergslagsbanan, Gstr</t>
+          <t>Forsbacka, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603184</v>
+        <v>602827</v>
       </c>
       <c r="R2" t="n">
-        <v>6724127</v>
+        <v>6723876</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2018-12-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2018-12-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,17 +779,884 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>108305999</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Forsbacka, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>602819</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6723892</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-12-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-12-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>72229442</v>
+      </c>
+      <c r="B4" t="n">
+        <v>40541</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100694</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knytlingsäckmal</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Coleophora scabrida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Toll, 1959</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Forsbacka sopstation, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>602958</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6723982</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-07-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-07-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>100-150 larver på en serviceväg till en elcentral vid järnvägsbanken.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Sahlin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>108306006</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57563</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gråtrut</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Larus argentatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pontoppidan, 1763</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Forsbacka, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>602813</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6723863</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-12-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-12-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108305997</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57569</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102967</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Havstrut</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Larus marinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Forsbacka, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>602820</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6723882</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-12-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-12-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129523499</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>603184</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6724127</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Elin Lönnberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Sanna Pousar</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Bergslagsbanan fågelinventeringar C240036</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>108306001</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Forsbacka, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>602827</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6723876</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-12-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-12-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>108306010</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Forsbacka, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>602812</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6723871</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2018-12-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2018-12-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Hallqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>92807323</v>
+      </c>
+      <c r="B10" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Forsbacka avfallsstation O, NV om järnväg, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>603341</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6724183</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2000-05-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2000-05-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kulturmark, grus/krosstenar utmed järnväg</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 202633N</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Birgitta Hellström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 11088-2026 artfynd.xlsx
+++ b/artfynd/A 11088-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108306000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108305999</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72229442</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108306006</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,6 +1249,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108305997</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523499</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108306001</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108306010</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,8 +1704,24 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92807323</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>